--- a/mica/NFDI4Health.ACTIVE_P2.R-dictionary.xlsx
+++ b/mica/NFDI4Health.ACTIVE_P2.R-dictionary.xlsx
@@ -7564,7 +7564,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7575,35 +7575,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Project1</t>
+          <t>index</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>valueType</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>valueType</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
@@ -7615,28 +7610,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C2">
+      <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Participant identification number</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Participant identification number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7648,28 +7640,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C3">
+      <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SEX</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7681,28 +7670,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B4" t="b">
-        <v>0</v>
-      </c>
-      <c r="C4">
+      <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AGE_BASE</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGE_BASE</t>
+          <t>Age at exposure measure [years]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Age at exposure measure [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7714,28 +7700,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B5" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5">
+      <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EDU_LEVEL</t>
+          <t>Highest level of education [ISCED 2011]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Highest level of education [ISCED 2011]</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7747,28 +7730,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B6" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6">
+      <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EMPLOY</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7780,28 +7760,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7">
+      <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IMMIGRATION</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IMMIGRATION</t>
+          <t>Immigration background</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Immigration background</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7813,28 +7790,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B8" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8">
+      <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TOT_PA_QX</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TOT_PA_QX</t>
+          <t>Physical activity from questionnaire data [MET-hr/day]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Physical activity from questionnaire data [MET-hr/day]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7846,28 +7820,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9">
+      <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TOT_PA_AC</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TOT_PA_AC</t>
+          <t>Physical activity from accelerometry data [MET-hr/day]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Physical activity from accelerometry data [MET-hr/day]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7879,28 +7850,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10">
+      <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SMOKE_ST</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SMOKE_ST</t>
+          <t>Smoking status</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smoking status</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7912,28 +7880,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B11" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11">
+      <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TOBACCO_PY</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TOBACCO_PY</t>
+          <t>Cumulative lifetime tobacco exposure  [pack years]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cumulative lifetime tobacco exposure  [pack years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7945,28 +7910,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B12" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12">
+      <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TOBACCO_D</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TOBACCO_D</t>
+          <t>Amount of daily tobacco smoked [g/day]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amount of daily tobacco smoked [g/day]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7978,28 +7940,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B13" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13">
+      <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AGE_SMOKE_QUIT</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AGE_SMOKE_QUIT</t>
+          <t>Age at time of quitting smoking [years]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Age at time of quitting smoking [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8011,28 +7970,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C14">
+      <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MED_SUPPL</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MED_SUPPL</t>
+          <t>Regular use of  vitamin/multivitamin supplements</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Regular use of  vitamin/multivitamin supplements</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8044,28 +8000,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B15" t="b">
-        <v>0</v>
-      </c>
-      <c r="C15">
+      <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MENOPAUSE</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MENOPAUSE</t>
+          <t>Menopause status</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Menopause status</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8077,28 +8030,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B16" t="b">
-        <v>0</v>
-      </c>
-      <c r="C16">
+      <c r="B16">
         <v>15</v>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HRT</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HRT</t>
+          <t>Hormone replacement therapy</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hormone replacement therapy</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8110,28 +8060,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B17" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17">
+      <c r="B17">
         <v>16</v>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CONTRACEPTIVE</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CONTRACEPTIVE</t>
+          <t>Use of contraceptive pills or injections [years]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Use of contraceptive pills or injections [years]</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8143,28 +8090,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B18" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18">
+      <c r="B18">
         <v>17</v>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LIVE_BIRTHS</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LIVE_BIRTHS</t>
+          <t>Number of live births given [Nr. of birth]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Number of live births given [Nr. of birth]</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8176,28 +8120,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B19" t="b">
-        <v>0</v>
-      </c>
-      <c r="C19">
+      <c r="B19">
         <v>18</v>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AGE_FIRST_BIRTH</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AGE_FIRST_BIRTH</t>
+          <t>Age at the first given birth [years]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Age at the first given birth [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8209,28 +8150,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B20" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20">
+      <c r="B20">
         <v>19</v>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TG</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>Triglycerides measured from blood samples [mmol/L]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Triglycerides measured from blood samples [mmol/L]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8242,28 +8180,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B21" t="b">
-        <v>0</v>
-      </c>
-      <c r="C21">
+      <c r="B21">
         <v>20</v>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CHOL</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CHOL</t>
+          <t>Total cholesterol measured from blood samples [mmol/L]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Total cholesterol measured from blood samples [mmol/L]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8275,28 +8210,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B22" t="b">
-        <v>0</v>
-      </c>
-      <c r="C22">
+      <c r="B22">
         <v>21</v>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LDL</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LDL</t>
+          <t>LDL cholesterol measured from blood samples [mmol/L]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LDL cholesterol measured from blood samples [mmol/L]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8308,28 +8240,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B23" t="b">
-        <v>0</v>
-      </c>
-      <c r="C23">
+      <c r="B23">
         <v>22</v>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HDL</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HDL</t>
+          <t>HDL cholesterol measured from blood samples [mmol/L]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HDL cholesterol measured from blood samples [mmol/L]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8341,28 +8270,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B24" t="b">
-        <v>0</v>
-      </c>
-      <c r="C24">
+      <c r="B24">
         <v>23</v>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PREV_DIAB</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PREV_DIAB</t>
+          <t>History of diabetes</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>History of diabetes</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8374,28 +8300,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B25" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25">
+      <c r="B25">
         <v>24</v>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PREV_HYP</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PREV_HYP</t>
+          <t>History of hypertension</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>History of hypertension</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8407,28 +8330,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B26" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26">
+      <c r="B26">
         <v>25</v>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PREV_CVD</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PREV_CVD</t>
+          <t>History of cardiovascular disease</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>History of cardiovascular disease</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8440,28 +8360,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B27" t="b">
-        <v>0</v>
-      </c>
-      <c r="C27">
+      <c r="B27">
         <v>26</v>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PREV_CANCER</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PREV_CANCER</t>
+          <t>History of cancer</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>History of cancer</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8473,28 +8390,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B28" t="b">
-        <v>0</v>
-      </c>
-      <c r="C28">
+      <c r="B28">
         <v>27</v>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FAM1_CHD_STROKE</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FAM1_CHD_STROKE</t>
+          <t>First degree family history of premature CHD and stroke</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>First degree family history of premature CHD and stroke</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8506,28 +8420,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B29" t="b">
-        <v>0</v>
-      </c>
-      <c r="C29">
+      <c r="B29">
         <v>28</v>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FAM1_DIAB2</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FAM1_DIAB2</t>
+          <t>First degree family history of T2D</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>First degree family history of T2D</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8539,28 +8450,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B30" t="b">
-        <v>0</v>
-      </c>
-      <c r="C30">
+      <c r="B30">
         <v>29</v>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FAM1_CANCER</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FAM1_CANCER</t>
+          <t>First degree family history of cancer</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>First degree family history of cancer</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8572,28 +8480,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B31" t="b">
-        <v>0</v>
-      </c>
-      <c r="C31">
+      <c r="B31">
         <v>30</v>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DRE_SCREEN</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DRE_SCREEN</t>
+          <t>Screening, DRE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Screening, DRE</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8605,28 +8510,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B32" t="b">
-        <v>0</v>
-      </c>
-      <c r="C32">
+      <c r="B32">
         <v>31</v>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PSA_SCREEN</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PSA_SCREEN</t>
+          <t>Screening, PSA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Screening, PSA</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8638,28 +8540,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B33" t="b">
-        <v>0</v>
-      </c>
-      <c r="C33">
+      <c r="B33">
         <v>32</v>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FOBT_SCREEN</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FOBT_SCREEN</t>
+          <t>Screening, FOBT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Screening, FOBT</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8671,28 +8570,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B34" t="b">
-        <v>0</v>
-      </c>
-      <c r="C34">
+      <c r="B34">
         <v>33</v>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>COL_SCREEN</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>COL_SCREEN</t>
+          <t>Screening, colonoscopy</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Screening, colonoscopy</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8704,28 +8600,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B35" t="b">
-        <v>0</v>
-      </c>
-      <c r="C35">
+      <c r="B35">
         <v>34</v>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MELANOMA_SCREEN</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MELANOMA_SCREEN</t>
+          <t>Screening, skin cancer</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Screening, skin cancer</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8737,28 +8630,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B36" t="b">
-        <v>0</v>
-      </c>
-      <c r="C36">
+      <c r="B36">
         <v>35</v>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MAMMO_SCREEN</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MAMMO_SCREEN</t>
+          <t>Screening, mammography</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Screening, mammography</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8770,28 +8660,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B37" t="b">
-        <v>0</v>
-      </c>
-      <c r="C37">
+      <c r="B37">
         <v>36</v>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CERVICAL_SCREEN</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CERVICAL_SCREEN</t>
+          <t>Screening cervical, smear test</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Screening cervical, smear test</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8803,28 +8690,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B38" t="b">
-        <v>0</v>
-      </c>
-      <c r="C38">
+      <c r="B38">
         <v>37</v>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MED_STAT</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MED_STAT</t>
+          <t>Regular use of statins</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Regular use of statins</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8836,28 +8720,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B39" t="b">
-        <v>0</v>
-      </c>
-      <c r="C39">
+      <c r="B39">
         <v>38</v>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MED_NSAID</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MED_NSAID</t>
+          <t>Regular use of non-steroidal anti-inflammatory drugs</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Regular use of non-steroidal anti-inflammatory drugs</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8869,28 +8750,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B40" t="b">
-        <v>0</v>
-      </c>
-      <c r="C40">
+      <c r="B40">
         <v>39</v>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INC_CVD</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>INC_CVD</t>
+          <t>CVD event during follow-up</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CVD event during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8902,28 +8780,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B41" t="b">
-        <v>0</v>
-      </c>
-      <c r="C41">
+      <c r="B41">
         <v>40</v>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AGE_CVD</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AGE_CVD</t>
+          <t>Age at diagnosis of CVD [years]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Age at diagnosis of CVD [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8935,28 +8810,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B42" t="b">
-        <v>0</v>
-      </c>
-      <c r="C42">
+      <c r="B42">
         <v>41</v>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INC_ANGINA</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INC_ANGINA</t>
+          <t>Angina pectoris event during follow-up</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Angina pectoris event during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8968,28 +8840,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B43" t="b">
-        <v>0</v>
-      </c>
-      <c r="C43">
+      <c r="B43">
         <v>42</v>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AGE_ANGINA</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AGE_ANGINA</t>
+          <t>Age at diagnosis of angina pectoris [years]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Age at diagnosis of angina pectoris [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9001,28 +8870,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B44" t="b">
-        <v>0</v>
-      </c>
-      <c r="C44">
+      <c r="B44">
         <v>43</v>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INC_MI</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INC_MI</t>
+          <t>Myocardial infarction during follow-up</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Myocardial infarction during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9034,28 +8900,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B45" t="b">
-        <v>0</v>
-      </c>
-      <c r="C45">
+      <c r="B45">
         <v>44</v>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AGE_MI</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AGE_MI</t>
+          <t>Age at diagnosis of myocardial infarction [years]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Age at diagnosis of myocardial infarction [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9067,28 +8930,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B46" t="b">
-        <v>0</v>
-      </c>
-      <c r="C46">
+      <c r="B46">
         <v>45</v>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INC_STR</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INC_STR</t>
+          <t>Stroke during follow-up</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stroke during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9100,28 +8960,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B47" t="b">
-        <v>0</v>
-      </c>
-      <c r="C47">
+      <c r="B47">
         <v>46</v>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AGE_STR</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AGE_STR</t>
+          <t>Age at diagnosis of stroke [years]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Age at diagnosis of stroke [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9133,28 +8990,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B48" t="b">
-        <v>0</v>
-      </c>
-      <c r="C48">
+      <c r="B48">
         <v>47</v>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INC_ISC_STR</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INC_ISC_STR</t>
+          <t>Cerebral infarction (ischaemic stroke) during follow-up</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cerebral infarction (ischaemic stroke) during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9166,28 +9020,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B49" t="b">
-        <v>0</v>
-      </c>
-      <c r="C49">
+      <c r="B49">
         <v>48</v>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AGE_ISC_STR</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AGE_ISC_STR</t>
+          <t>Age at diagnosis of cerebral infarction (ischaemic stroke) [years]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Age at diagnosis of cerebral infarction (ischaemic stroke) [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9199,28 +9050,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C50">
+      <c r="B50">
         <v>49</v>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INC_HAEMO_STR</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INC_HAEMO_STR</t>
+          <t>Haemorrhagic stroke during follow-up</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Haemorrhagic stroke during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9232,28 +9080,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B51" t="b">
-        <v>0</v>
-      </c>
-      <c r="C51">
+      <c r="B51">
         <v>50</v>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AGE_HAEMO_STR</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AGE_HAEMO_STR</t>
+          <t>Age at diagnosis of haemorrhagic stroke [years]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Age at diagnosis of haemorrhagic stroke [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9265,28 +9110,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B52" t="b">
-        <v>0</v>
-      </c>
-      <c r="C52">
+      <c r="B52">
         <v>51</v>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INC_HYP</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INC_HYP</t>
+          <t>Essential hypertension during follow-up</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Essential hypertension during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9298,28 +9140,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B53" t="b">
-        <v>0</v>
-      </c>
-      <c r="C53">
+      <c r="B53">
         <v>52</v>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AGE_HYP</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AGE_HYP</t>
+          <t>Age at diagnosis of essential hypertension [years]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Age at diagnosis of essential hypertension [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9331,28 +9170,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B54" t="b">
-        <v>0</v>
-      </c>
-      <c r="C54">
+      <c r="B54">
         <v>53</v>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INC_HF</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>INC_HF</t>
+          <t>Heart failure during follow-up</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heart failure during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9364,28 +9200,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B55" t="b">
-        <v>0</v>
-      </c>
-      <c r="C55">
+      <c r="B55">
         <v>54</v>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AGE_HF</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AGE_HF</t>
+          <t>Age at diagnosis of heart failure [years]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Age at diagnosis of heart failure [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9397,28 +9230,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B56" t="b">
-        <v>0</v>
-      </c>
-      <c r="C56">
+      <c r="B56">
         <v>55</v>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>INC_DIAB2</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>INC_DIAB2</t>
+          <t>Diabetes mellitus type 2 during follow-up</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Diabetes mellitus type 2 during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9430,28 +9260,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B57" t="b">
-        <v>0</v>
-      </c>
-      <c r="C57">
+      <c r="B57">
         <v>56</v>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AGE_DIAB2</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AGE_DIAB2</t>
+          <t>Age at diagnosis of diabetes mellitus type 2 [years]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Age at diagnosis of diabetes mellitus type 2 [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9463,28 +9290,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B58" t="b">
-        <v>0</v>
-      </c>
-      <c r="C58">
+      <c r="B58">
         <v>57</v>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>INC_CANCER</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>INC_CANCER</t>
+          <t>Cancer during follow-up</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cancer during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9496,28 +9320,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B59" t="b">
-        <v>0</v>
-      </c>
-      <c r="C59">
+      <c r="B59">
         <v>58</v>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TYPE_CANCER</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TYPE_CANCER</t>
+          <t>Type of Cancer (ICD 10, 3 digits,e.g. C18.3)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Type of Cancer (ICD 10, 3 digits,e.g. C18.3)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9529,28 +9350,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B60" t="b">
-        <v>0</v>
-      </c>
-      <c r="C60">
+      <c r="B60">
         <v>59</v>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AGE_CANCER</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AGE_CANCER</t>
+          <t>Age at diagnosis of cancer [years]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Age at diagnosis of cancer [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9562,28 +9380,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B61" t="b">
-        <v>0</v>
-      </c>
-      <c r="C61">
+      <c r="B61">
         <v>60</v>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VITAL_ST</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VITAL_ST</t>
+          <t>Vital status at the end of mortality follow-up</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vital status at the end of mortality follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9595,28 +9410,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B62" t="b">
-        <v>0</v>
-      </c>
-      <c r="C62">
+      <c r="B62">
         <v>61</v>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AGE_DEATH</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AGE_DEATH</t>
+          <t>Age at time of death [years]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Age at time of death [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9628,28 +9440,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B63" t="b">
-        <v>0</v>
-      </c>
-      <c r="C63">
+      <c r="B63">
         <v>62</v>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CVD</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VITAL_ST_CVD</t>
+          <t>Vital status at the end of CVD mortality follow-up</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vital status at the end of CVD mortality follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9661,28 +9470,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B64" t="b">
-        <v>0</v>
-      </c>
-      <c r="C64">
+      <c r="B64">
         <v>63</v>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CANCER</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VITAL_ST_CANCER</t>
+          <t>Vital status at the end of cancer mortality follow-up</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vital status at the end of cancer mortality follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9694,28 +9500,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B65" t="b">
-        <v>0</v>
-      </c>
-      <c r="C65">
+      <c r="B65">
         <v>64</v>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AGE_FUP</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AGE_FUP</t>
+          <t>Age at end of follow-up [years]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Age at end of follow-up [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9727,28 +9530,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B66" t="b">
-        <v>0</v>
-      </c>
-      <c r="C66">
+      <c r="B66">
         <v>65</v>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BMI</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>Body Mass Index at baseline [kg/m²]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Body Mass Index at baseline [kg/m²]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9760,28 +9560,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B67" t="b">
-        <v>0</v>
-      </c>
-      <c r="C67">
+      <c r="B67">
         <v>66</v>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BMI_FUP</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BMI_FUP</t>
+          <t>Body Mass Index at follow-up [kg/m²]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Body Mass Index at follow-up [kg/m²]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9793,28 +9590,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B68" t="b">
-        <v>0</v>
-      </c>
-      <c r="C68">
+      <c r="B68">
         <v>67</v>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BMI_SDS</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BMI_SDS</t>
+          <t>Body Mass Index Standard Deviation Score at baseline (children studies)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Body Mass Index Standard Deviation Score at baseline (children studies)</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9826,28 +9620,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B69" t="b">
-        <v>0</v>
-      </c>
-      <c r="C69">
+      <c r="B69">
         <v>68</v>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BMI_SDS_FUP</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BMI_SDS_FUP</t>
+          <t>Body Mass Index Standard Deviation Score at follow-up (children studies)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Body Mass Index Standard Deviation Score at follow-up (children studies)</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9859,28 +9650,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B70" t="b">
-        <v>0</v>
-      </c>
-      <c r="C70">
+      <c r="B70">
         <v>69</v>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>WAIST_FUP</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>WAIST_FUP</t>
+          <t>Waist circumference at follow-up [cm]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Waist circumference at follow-up [cm]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9892,28 +9680,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B71" t="b">
-        <v>0</v>
-      </c>
-      <c r="C71">
+      <c r="B71">
         <v>70</v>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>WAIST</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>WAIST</t>
+          <t>Waist circumference at baseline [cm]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Waist circumference at baseline [cm]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9925,28 +9710,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B72" t="b">
-        <v>0</v>
-      </c>
-      <c r="C72">
+      <c r="B72">
         <v>71</v>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HIP</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>HIP</t>
+          <t>Hip circumference at baseline [cm]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hip circumference at baseline [cm]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9958,28 +9740,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B73" t="b">
-        <v>0</v>
-      </c>
-      <c r="C73">
+      <c r="B73">
         <v>72</v>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HIP_FUP</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HIP_FUP</t>
+          <t>Hip circumference at follow-up [cm]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hip circumference at follow-up [cm]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9991,28 +9770,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B74" t="b">
-        <v>0</v>
-      </c>
-      <c r="C74">
+      <c r="B74">
         <v>73</v>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FMI_FUP</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>FMI_FUP</t>
+          <t>Fat mass index at follow-up  [kg/m²]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fat mass index at follow-up  [kg/m²]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10024,28 +9800,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B75" t="b">
-        <v>0</v>
-      </c>
-      <c r="C75">
+      <c r="B75">
         <v>74</v>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FMI</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>FMI</t>
+          <t>Fat mass index at baseline  [kg/m²]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fat mass index at baseline  [kg/m²]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10057,28 +9830,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B76" t="b">
-        <v>0</v>
-      </c>
-      <c r="C76">
+      <c r="B76">
         <v>75</v>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BODY_FAT_FUP</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BODY_FAT_FUP</t>
+          <t>Body fat precent at follow-up [%]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Body fat precent at follow-up [%]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10090,28 +9860,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B77" t="b">
-        <v>0</v>
-      </c>
-      <c r="C77">
+      <c r="B77">
         <v>76</v>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BODY_FAT</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BODY_FAT</t>
+          <t>Body fat precent at baseline  [%]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Body fat precent at baseline  [%]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10123,28 +9890,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B78" t="b">
-        <v>0</v>
-      </c>
-      <c r="C78">
+      <c r="B78">
         <v>77</v>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AGE_ANTH_FUP</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AGE_ANTH_FUP</t>
+          <t>Age at anthropometric measurement at follow-up [years]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Age at anthropometric measurement at follow-up [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10156,28 +9920,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B79" t="b">
-        <v>0</v>
-      </c>
-      <c r="C79">
+      <c r="B79">
         <v>78</v>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>Energy intake [kcal/d]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Energy intake [kcal/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10189,28 +9950,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B80" t="b">
-        <v>0</v>
-      </c>
-      <c r="C80">
+      <c r="B80">
         <v>79</v>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CARB</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CARB</t>
+          <t>Carbohydrate intake [g/d]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Carbohydrate intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10222,28 +9980,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B81" t="b">
-        <v>0</v>
-      </c>
-      <c r="C81">
+      <c r="B81">
         <v>80</v>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PROT</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PROT</t>
+          <t>Protein intake [g/d]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Protein intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10255,28 +10010,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B82" t="b">
-        <v>0</v>
-      </c>
-      <c r="C82">
+      <c r="B82">
         <v>81</v>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>FAT</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FAT</t>
+          <t>Fat intake [g/d]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fat intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10288,28 +10040,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B83" t="b">
-        <v>0</v>
-      </c>
-      <c r="C83">
+      <c r="B83">
         <v>82</v>
       </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ALC</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>Alcohol intake [g/d]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Alcohol intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10321,28 +10070,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B84" t="b">
-        <v>0</v>
-      </c>
-      <c r="C84">
+      <c r="B84">
         <v>83</v>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FIBER</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FIBER</t>
+          <t>Dietary fiber intake [g/d]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dietary fiber intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10354,28 +10100,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B85" t="b">
-        <v>0</v>
-      </c>
-      <c r="C85">
+      <c r="B85">
         <v>84</v>
       </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SFA</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SFA</t>
+          <t>Saturated fat intake [g/d]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saturated fat intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10387,28 +10130,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B86" t="b">
-        <v>0</v>
-      </c>
-      <c r="C86">
+      <c r="B86">
         <v>85</v>
       </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MUFA</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MUFA</t>
+          <t>Monounsaturated fat intake [g/d]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Monounsaturated fat intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10420,28 +10160,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B87" t="b">
-        <v>0</v>
-      </c>
-      <c r="C87">
+      <c r="B87">
         <v>86</v>
       </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PUFA</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PUFA</t>
+          <t>Polyunsaturated fat intake [g/d]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Polyunsaturated fat intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10453,28 +10190,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B88" t="b">
-        <v>0</v>
-      </c>
-      <c r="C88">
+      <c r="B88">
         <v>87</v>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TOT_SUGARS</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TOT_SUGARS</t>
+          <t>Total sugar intake [g/d]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Total sugar intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10486,28 +10220,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B89" t="b">
-        <v>0</v>
-      </c>
-      <c r="C89">
+      <c r="B89">
         <v>88</v>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ADD_SUGARS</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ADD_SUGARS</t>
+          <t>Added sugar intake [g/d]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Added sugar intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10519,28 +10250,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B90" t="b">
-        <v>0</v>
-      </c>
-      <c r="C90">
+      <c r="B90">
         <v>89</v>
       </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>FREE_SUGARS</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>FREE_SUGARS</t>
+          <t>Free sugar intake [g/d]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sugar intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10552,28 +10280,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B91" t="b">
-        <v>0</v>
-      </c>
-      <c r="C91">
+      <c r="B91">
         <v>90</v>
       </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>GLUC</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GLUC</t>
+          <t>Glucose intake [g/d]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Glucose intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10585,28 +10310,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B92" t="b">
-        <v>0</v>
-      </c>
-      <c r="C92">
+      <c r="B92">
         <v>91</v>
       </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>FRUC</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>FRUC</t>
+          <t>Fructose intake [g/d]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Fructose intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10618,28 +10340,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B93" t="b">
-        <v>0</v>
-      </c>
-      <c r="C93">
+      <c r="B93">
         <v>92</v>
       </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GI</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>GI</t>
+          <t>Daily glycaemic index</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Daily glycaemic index</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10651,28 +10370,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B94" t="b">
-        <v>0</v>
-      </c>
-      <c r="C94">
+      <c r="B94">
         <v>93</v>
       </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Daily glycaemic load</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Daily glycaemic load</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10684,28 +10400,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B95" t="b">
-        <v>0</v>
-      </c>
-      <c r="C95">
+      <c r="B95">
         <v>94</v>
       </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SODIUM</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SODIUM</t>
+          <t>Sodium intake [mg/d]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sodium intake [mg/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10717,28 +10430,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B96" t="b">
-        <v>0</v>
-      </c>
-      <c r="C96">
+      <c r="B96">
         <v>95</v>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SOD_POT_RATIO</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SOD_POT_RATIO</t>
+          <t>Sodium to potassium intake ratio</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sodium to potassium intake ratio</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10750,28 +10460,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B97" t="b">
-        <v>0</v>
-      </c>
-      <c r="C97">
+      <c r="B97">
         <v>96</v>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SUGAR_CONFECT_11</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SUGAR_CONFECT_11</t>
+          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10783,28 +10490,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B98" t="b">
-        <v>0</v>
-      </c>
-      <c r="C98">
+      <c r="B98">
         <v>97</v>
       </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CAKES_12</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CAKES_12</t>
+          <t>Intake of cakes and fine bakery products [g/d]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Intake of cakes and fine bakery products [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10816,28 +10520,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B99" t="b">
-        <v>0</v>
-      </c>
-      <c r="C99">
+      <c r="B99">
         <v>98</v>
       </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>FRUITVEG_JUICE_1301</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FRUITVEG_JUICE_1301</t>
+          <t>Intake of fruit and vegetable juices [g/d]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Intake of fruit and vegetable juices [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10849,28 +10550,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B100" t="b">
-        <v>0</v>
-      </c>
-      <c r="C100">
+      <c r="B100">
         <v>99</v>
       </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SOFTDRINKS_1302</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SOFTDRINKS_1302</t>
+          <t>Intake of soft drinks [g/d]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Intake of soft drinks [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10882,28 +10580,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B101" t="b">
-        <v>0</v>
-      </c>
-      <c r="C101">
+      <c r="B101">
         <v>100</v>
       </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ART_SWEETENER_170201</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ART_SWEETENER_170201</t>
+          <t>Intake of artificial sweeteners (e.g., aspartam, saccharine) [g/d]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Intake of artificial sweeteners (e.g., aspartam, saccharine) [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10915,28 +10610,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B102" t="b">
-        <v>0</v>
-      </c>
-      <c r="C102">
+      <c r="B102">
         <v>101</v>
       </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>VEGETABLES_02</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VEGETABLES_02</t>
+          <t>Vegetable intake [g/d]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vegetable intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10948,28 +10640,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B103" t="b">
-        <v>0</v>
-      </c>
-      <c r="C103">
+      <c r="B103">
         <v>102</v>
       </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>LEGUMES_TOT_03</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LEGUMES_TOT_03</t>
+          <t>Total legumes intake [g/d]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Total legumes intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10981,28 +10670,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B104" t="b">
-        <v>0</v>
-      </c>
-      <c r="C104">
+      <c r="B104">
         <v>103</v>
       </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>FRUITS_TOT_04</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>FRUITS_TOT_04</t>
+          <t>Total fruit intake [g/d]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Total fruit intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11014,28 +10700,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B105" t="b">
-        <v>0</v>
-      </c>
-      <c r="C105">
+      <c r="B105">
         <v>104</v>
       </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>RED_MEAT_0701</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>RED_MEAT_0701</t>
+          <t>Intake of red meat (mammals meat) [g/d]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Intake of red meat (mammals meat) [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11047,28 +10730,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B106" t="b">
-        <v>0</v>
-      </c>
-      <c r="C106">
+      <c r="B106">
         <v>105</v>
       </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>PROCMEAT_0704</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PROCMEAT_0704</t>
+          <t>Intake of processed or preserved meat [g/d]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Intake of processed or preserved meat [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11080,28 +10760,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B107" t="b">
-        <v>0</v>
-      </c>
-      <c r="C107">
+      <c r="B107">
         <v>106</v>
       </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>COFFEE_130301</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>COFFEE_130301</t>
+          <t>Coffee intake [g/d]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Coffee intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11113,28 +10790,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B108" t="b">
-        <v>0</v>
-      </c>
-      <c r="C108">
+      <c r="B108">
         <v>107</v>
       </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>TEA_130302</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>TEA_130302</t>
+          <t>Tea intake [g/d]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tea intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11146,28 +10820,25 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B109" t="b">
-        <v>0</v>
-      </c>
-      <c r="C109">
+      <c r="B109">
         <v>108</v>
       </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DIETARY_ASSESS_INSTR</t>
+          <t>Dietary Assessment Instrument</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dietary Assessment Instrument</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/mica/NFDI4Health.ACTIVE_P2.R-dictionary.xlsx
+++ b/mica/NFDI4Health.ACTIVE_P2.R-dictionary.xlsx
@@ -7564,7 +7564,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7575,30 +7575,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>variable</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>valueType</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
@@ -7610,25 +7605,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SEX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Participant identification number</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7640,25 +7630,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SEX</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SEX</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7670,25 +7655,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B4">
-        <v>3</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AGE_BASE</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Age at exposure measure [years]</t>
-        </is>
+          <t>Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7700,25 +7680,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B5">
-        <v>4</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EDU_LEVEL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Highest level of education [ISCED 2011]</t>
-        </is>
+          <t>Primary Education</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7730,25 +7705,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B6">
-        <v>5</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EMPLOY</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
+          <t>Lower Secondary Education</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7760,25 +7730,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B7">
-        <v>6</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IMMIGRATION</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Immigration background</t>
-        </is>
+          <t>Upper Secondary Education</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7790,25 +7755,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B8">
-        <v>7</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TOT_PA_QX</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Physical activity from questionnaire data [MET-hr/day]</t>
-        </is>
+          <t>Post-secondary non-tertiary education</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7820,25 +7780,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B9">
-        <v>8</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOT_PA_AC</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Physical activity from accelerometry data [MET-hr/day]</t>
-        </is>
+          <t>Short-Cycle Tertiary Education</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7850,25 +7805,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B10">
-        <v>9</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SMOKE_ST</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Smoking status</t>
-        </is>
+          <t>Bachelor's or equivalent level</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7880,25 +7830,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B11">
-        <v>10</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOBACCO_PY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Cumulative lifetime tobacco exposure  [pack years]</t>
-        </is>
+          <t>Master's or equivalent level</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>7</v>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7910,25 +7855,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B12">
-        <v>11</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOBACCO_D</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Amount of daily tobacco smoked [g/day]</t>
-        </is>
+          <t>Doctoral or equivalent level</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>8</v>
       </c>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7940,25 +7880,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B13">
-        <v>12</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AGE_SMOKE_QUIT</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Age at time of quitting smoking [years]</t>
-        </is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7970,25 +7905,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B14">
-        <v>13</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MED_SUPPL</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Regular use of  vitamin/multivitamin supplements</t>
-        </is>
+          <t>employed-full time</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8000,25 +7930,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B15">
-        <v>14</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MENOPAUSE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Menopause status</t>
-        </is>
+          <t>employed-part time</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8030,25 +7955,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B16">
-        <v>15</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HRT</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Hormone replacement therapy</t>
-        </is>
+          <t>housewife</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8060,25 +7980,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B17">
-        <v>16</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CONTRACEPTIVE</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Use of contraceptive pills or injections [years]</t>
-        </is>
+          <t>retired</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>4</v>
       </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8090,25 +8005,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B18">
-        <v>17</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LIVE_BIRTHS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Number of live births given [Nr. of birth]</t>
-        </is>
+          <t>unemployed</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>5</v>
       </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8120,25 +8030,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B19">
-        <v>18</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AGE_FIRST_BIRTH</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Age at the first given birth [years]</t>
-        </is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>6</v>
       </c>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8150,25 +8055,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B20">
-        <v>19</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TG</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Triglycerides measured from blood samples [mmol/L]</t>
-        </is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>7</v>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8180,25 +8080,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B21">
-        <v>20</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IMMIGRATION</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CHOL</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Total cholesterol measured from blood samples [mmol/L]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8210,25 +8105,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B22">
-        <v>21</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IMMIGRATION</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LDL</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LDL cholesterol measured from blood samples [mmol/L]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8240,25 +8130,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B23">
-        <v>22</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SMOKE_ST</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HDL</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>HDL cholesterol measured from blood samples [mmol/L]</t>
-        </is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8270,25 +8155,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B24">
-        <v>23</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SMOKE_ST</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PREV_DIAB</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>History of diabetes</t>
-        </is>
+          <t>former</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>2</v>
       </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8300,25 +8180,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B25">
-        <v>24</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SMOKE_ST</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PREV_HYP</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>History of hypertension</t>
-        </is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8330,25 +8205,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B26">
-        <v>25</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SMOKE_ST</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PREV_CVD</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>History of cardiovascular disease</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>4</v>
       </c>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8360,25 +8230,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B27">
-        <v>26</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MED_SUPPL</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PREV_CANCER</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>History of cancer</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8390,25 +8255,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B28">
-        <v>27</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MED_SUPPL</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FAM1_CHD_STROKE</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>First degree family history of premature CHD and stroke</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8420,25 +8280,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B29">
-        <v>28</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MENOPAUSE</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FAM1_DIAB2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>First degree family history of T2D</t>
-        </is>
+          <t>premenopausal</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8450,25 +8305,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B30">
-        <v>29</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MENOPAUSE</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FAM1_CANCER</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>First degree family history of cancer</t>
-        </is>
+          <t>postmenopausal</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8480,25 +8330,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B31">
-        <v>30</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MENOPAUSE</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DRE_SCREEN</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Screening, DRE</t>
-        </is>
+          <t>perimenopausal</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>2</v>
       </c>
       <c r="E31" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8510,25 +8355,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B32">
-        <v>31</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MENOPAUSE</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PSA_SCREEN</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Screening, PSA</t>
-        </is>
+          <t>surgical postmenopausal (bilateral ovariectomy)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>3</v>
       </c>
       <c r="E32" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8540,25 +8380,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B33">
-        <v>32</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HRT</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FOBT_SCREEN</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Screening, FOBT</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8570,25 +8405,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B34">
-        <v>33</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HRT</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COL_SCREEN</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Screening, colonoscopy</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8600,25 +8430,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B35">
-        <v>34</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PREV_DIAB</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MELANOMA_SCREEN</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Screening, skin cancer</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8630,25 +8455,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B36">
-        <v>35</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PREV_DIAB</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MAMMO_SCREEN</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Screening, mammography</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8660,25 +8480,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B37">
-        <v>36</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PREV_HYP</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CERVICAL_SCREEN</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Screening cervical, smear test</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8690,25 +8505,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B38">
-        <v>37</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PREV_HYP</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MED_STAT</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Regular use of statins</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8720,25 +8530,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B39">
-        <v>38</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PREV_CVD</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MED_NSAID</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Regular use of non-steroidal anti-inflammatory drugs</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8750,25 +8555,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B40">
-        <v>39</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PREV_CVD</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INC_CVD</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>CVD event during follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8780,25 +8580,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B41">
-        <v>40</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PREV_CANCER</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AGE_CVD</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of CVD [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8810,25 +8605,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B42">
-        <v>41</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PREV_CANCER</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INC_ANGINA</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Angina pectoris event during follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>1</v>
       </c>
       <c r="E42" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8840,25 +8630,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B43">
-        <v>42</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FAM1_CHD_STROKE</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AGE_ANGINA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of angina pectoris [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8870,25 +8655,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B44">
-        <v>43</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FAM1_CHD_STROKE</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INC_MI</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Myocardial infarction during follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8900,25 +8680,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B45">
-        <v>44</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FAM1_CHD_STROKE</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AGE_MI</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of myocardial infarction [years]</t>
-        </is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>2</v>
       </c>
       <c r="E45" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8930,25 +8705,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B46">
-        <v>45</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FAM1_DIAB2</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INC_STR</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Stroke during follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8960,25 +8730,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B47">
-        <v>46</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FAM1_DIAB2</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AGE_STR</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of stroke [years]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8990,25 +8755,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B48">
-        <v>47</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FAM1_DIAB2</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INC_ISC_STR</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Cerebral infarction (ischaemic stroke) during follow-up</t>
-        </is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>2</v>
       </c>
       <c r="E48" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9020,25 +8780,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B49">
-        <v>48</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FAM1_CANCER</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AGE_ISC_STR</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of cerebral infarction (ischaemic stroke) [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9050,25 +8805,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B50">
-        <v>49</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FAM1_CANCER</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INC_HAEMO_STR</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Haemorrhagic stroke during follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>1</v>
       </c>
       <c r="E50" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9080,25 +8830,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B51">
-        <v>50</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FAM1_CANCER</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AGE_HAEMO_STR</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of haemorrhagic stroke [years]</t>
-        </is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>2</v>
       </c>
       <c r="E51" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9110,25 +8855,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B52">
-        <v>51</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>DRE_SCREEN</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INC_HYP</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Essential hypertension during follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>0</v>
       </c>
       <c r="E52" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9140,25 +8880,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B53">
-        <v>52</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>DRE_SCREEN</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AGE_HYP</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of essential hypertension [years]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9170,25 +8905,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B54">
-        <v>53</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PSA_SCREEN</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>INC_HF</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Heart failure during follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>0</v>
       </c>
       <c r="E54" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9200,25 +8930,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B55">
-        <v>54</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PSA_SCREEN</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AGE_HF</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of heart failure [years]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>1</v>
       </c>
       <c r="E55" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9230,25 +8955,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B56">
-        <v>55</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FOBT_SCREEN</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INC_DIAB2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Diabetes mellitus type 2 during follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>0</v>
       </c>
       <c r="E56" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9260,25 +8980,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B57">
-        <v>56</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FOBT_SCREEN</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AGE_DIAB2</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of diabetes mellitus type 2 [years]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9290,25 +9005,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B58">
-        <v>57</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>COL_SCREEN</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>INC_CANCER</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Cancer during follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9320,25 +9030,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B59">
-        <v>58</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>COL_SCREEN</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TYPE_CANCER</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Type of Cancer (ICD 10, 3 digits,e.g. C18.3)</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>1</v>
       </c>
       <c r="E59" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9350,25 +9055,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B60">
-        <v>59</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MELANOMA_SCREEN</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AGE_CANCER</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of cancer [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9380,25 +9080,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B61">
-        <v>60</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MELANOMA_SCREEN</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VITAL_ST</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Vital status at the end of mortality follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D61">
+        <v>1</v>
       </c>
       <c r="E61" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9410,25 +9105,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B62">
-        <v>61</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MAMMO_SCREEN</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AGE_DEATH</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Age at time of death [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9440,25 +9130,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B63">
-        <v>62</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MAMMO_SCREEN</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VITAL_ST_CVD</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Vital status at the end of CVD mortality follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>1</v>
       </c>
       <c r="E63" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9470,25 +9155,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B64">
-        <v>63</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CERVICAL_SCREEN</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VITAL_ST_CANCER</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Vital status at the end of cancer mortality follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D64">
+        <v>0</v>
       </c>
       <c r="E64" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9500,25 +9180,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B65">
-        <v>64</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CERVICAL_SCREEN</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AGE_FUP</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Age at end of follow-up [years]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D65">
+        <v>1</v>
       </c>
       <c r="E65" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9530,25 +9205,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B66">
-        <v>65</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MED_STAT</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMI</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Body Mass Index at baseline [kg/m²]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D66">
+        <v>0</v>
       </c>
       <c r="E66" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9560,25 +9230,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B67">
-        <v>66</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MED_STAT</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMI_FUP</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Body Mass Index at follow-up [kg/m²]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>1</v>
       </c>
       <c r="E67" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9590,25 +9255,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B68">
-        <v>67</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MED_NSAID</t>
+        </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMI_SDS</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Body Mass Index Standard Deviation Score at baseline (children studies)</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>0</v>
       </c>
       <c r="E68" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9620,25 +9280,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B69">
-        <v>68</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MED_NSAID</t>
+        </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMI_SDS_FUP</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Body Mass Index Standard Deviation Score at follow-up (children studies)</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>1</v>
       </c>
       <c r="E69" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9650,25 +9305,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B70">
-        <v>69</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>INC_CVD</t>
+        </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WAIST_FUP</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Waist circumference at follow-up [cm]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>0</v>
       </c>
       <c r="E70" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9680,25 +9330,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B71">
-        <v>70</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>INC_CVD</t>
+        </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WAIST</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Waist circumference at baseline [cm]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>1</v>
       </c>
       <c r="E71" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9710,25 +9355,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B72">
-        <v>71</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>INC_ANGINA</t>
+        </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HIP</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Hip circumference at baseline [cm]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>0</v>
       </c>
       <c r="E72" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9740,25 +9380,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B73">
-        <v>72</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>INC_ANGINA</t>
+        </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HIP_FUP</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Hip circumference at follow-up [cm]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9770,25 +9405,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B74">
-        <v>73</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>INC_MI</t>
+        </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FMI_FUP</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Fat mass index at follow-up  [kg/m²]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>0</v>
       </c>
       <c r="E74" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9800,25 +9430,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B75">
-        <v>74</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INC_MI</t>
+        </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FMI</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Fat mass index at baseline  [kg/m²]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9830,25 +9455,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B76">
-        <v>75</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>INC_STR</t>
+        </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BODY_FAT_FUP</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Body fat precent at follow-up [%]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D76">
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9860,25 +9480,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B77">
-        <v>76</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>INC_STR</t>
+        </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BODY_FAT</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Body fat precent at baseline  [%]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9890,25 +9505,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B78">
-        <v>77</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>INC_ISC_STR</t>
+        </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AGE_ANTH_FUP</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Age at anthropometric measurement at follow-up [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D78">
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9920,25 +9530,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B79">
-        <v>78</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>INC_ISC_STR</t>
+        </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ENERGY</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Energy intake [kcal/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D79">
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9950,25 +9555,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B80">
-        <v>79</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>INC_HAEMO_STR</t>
+        </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CARB</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Carbohydrate intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D80">
+        <v>0</v>
       </c>
       <c r="E80" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9980,25 +9580,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B81">
-        <v>80</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>INC_HAEMO_STR</t>
+        </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PROT</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Protein intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D81">
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10010,25 +9605,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B82">
-        <v>81</v>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>INC_HYP</t>
+        </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FAT</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Fat intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D82">
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10040,25 +9630,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B83">
-        <v>82</v>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>INC_HYP</t>
+        </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ALC</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Alcohol intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D83">
+        <v>1</v>
       </c>
       <c r="E83" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10070,25 +9655,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B84">
-        <v>83</v>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>INC_HF</t>
+        </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FIBER</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Dietary fiber intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D84">
+        <v>0</v>
       </c>
       <c r="E84" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10100,25 +9680,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B85">
-        <v>84</v>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>INC_HF</t>
+        </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SFA</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Saturated fat intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D85">
+        <v>1</v>
       </c>
       <c r="E85" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10130,25 +9705,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B86">
-        <v>85</v>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>INC_DIAB2</t>
+        </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MUFA</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Monounsaturated fat intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D86">
+        <v>0</v>
       </c>
       <c r="E86" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10160,25 +9730,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B87">
-        <v>86</v>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>INC_DIAB2</t>
+        </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PUFA</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Polyunsaturated fat intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10190,25 +9755,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B88">
-        <v>87</v>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>INC_CANCER</t>
+        </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TOT_SUGARS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Total sugar intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D88">
+        <v>0</v>
       </c>
       <c r="E88" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10220,25 +9780,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B89">
-        <v>88</v>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>INC_CANCER</t>
+        </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ADD_SUGARS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Added sugar intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D89">
+        <v>1</v>
       </c>
       <c r="E89" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10250,25 +9805,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B90">
-        <v>89</v>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>VITAL_ST</t>
+        </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FREE_SUGARS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Free sugar intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D90">
+        <v>0</v>
       </c>
       <c r="E90" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10280,25 +9830,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B91">
-        <v>90</v>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>VITAL_ST</t>
+        </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GLUC</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Glucose intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D91">
+        <v>1</v>
       </c>
       <c r="E91" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10310,25 +9855,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B92">
-        <v>91</v>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CVD</t>
+        </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FRUC</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Fructose intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D92">
+        <v>0</v>
       </c>
       <c r="E92" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10340,25 +9880,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B93">
-        <v>92</v>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CVD</t>
+        </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GI</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Daily glycaemic index</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D93">
+        <v>1</v>
       </c>
       <c r="E93" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10370,25 +9905,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B94">
-        <v>93</v>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CANCER</t>
+        </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Daily glycaemic load</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D94">
+        <v>0</v>
       </c>
       <c r="E94" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10400,25 +9930,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B95">
-        <v>94</v>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CANCER</t>
+        </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SODIUM</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Sodium intake [mg/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D95">
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10430,25 +9955,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B96">
-        <v>95</v>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SOD_POT_RATIO</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Sodium to potassium intake ratio</t>
-        </is>
+          <t>FPQ (Food propensity questionnair without portion sizes)</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>0</v>
       </c>
       <c r="E96" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10460,25 +9980,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B97">
-        <v>96</v>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SUGAR_CONFECT_11</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
-        </is>
+          <t>FFQ (Food frequency questionnaire)</t>
+        </is>
+      </c>
+      <c r="D97">
+        <v>1</v>
       </c>
       <c r="E97" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10490,25 +10005,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B98">
-        <v>97</v>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAKES_12</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Intake of cakes and fine bakery products [g/d]</t>
-        </is>
+          <t>24HDR (24-h dietary recall)</t>
+        </is>
+      </c>
+      <c r="D98">
+        <v>2</v>
       </c>
       <c r="E98" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10520,25 +10030,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B99">
-        <v>98</v>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FRUITVEG_JUICE_1301</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Intake of fruit and vegetable juices [g/d]</t>
-        </is>
+          <t>3_d_FR_w (3-day weighing food record)</t>
+        </is>
+      </c>
+      <c r="D99">
+        <v>3</v>
       </c>
       <c r="E99" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10550,25 +10055,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B100">
-        <v>99</v>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SOFTDRINKS_1302</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Intake of soft drinks [g/d]</t>
-        </is>
+          <t>7_d_FR (7-day  food record; described portion sizes)</t>
+        </is>
+      </c>
+      <c r="D100">
+        <v>4</v>
       </c>
       <c r="E100" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10580,25 +10080,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B101">
-        <v>100</v>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ART_SWEETENER_170201</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Intake of artificial sweeteners (e.g., aspartam, saccharine) [g/d]</t>
-        </is>
+          <t>7_d_FR_w (7-day weighing food record)</t>
+        </is>
+      </c>
+      <c r="D101">
+        <v>5</v>
       </c>
       <c r="E101" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10610,235 +10105,20 @@
           <t>ACTIVE_P2</t>
         </is>
       </c>
-      <c r="B102">
-        <v>101</v>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VEGETABLES_02</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Vegetable intake [g/d]</t>
-        </is>
+          <t>24HFL_FFQ (24-h short food list combined with FFQ)</t>
+        </is>
+      </c>
+      <c r="D102">
+        <v>6</v>
       </c>
       <c r="E102" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>ACTIVE_P2</t>
-        </is>
-      </c>
-      <c r="B103">
-        <v>102</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>LEGUMES_TOT_03</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Total legumes intake [g/d]</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>ACTIVE_P2</t>
-        </is>
-      </c>
-      <c r="B104">
-        <v>103</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>FRUITS_TOT_04</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Total fruit intake [g/d]</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>ACTIVE_P2</t>
-        </is>
-      </c>
-      <c r="B105">
-        <v>104</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>RED_MEAT_0701</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Intake of red meat (mammals meat) [g/d]</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>ACTIVE_P2</t>
-        </is>
-      </c>
-      <c r="B106">
-        <v>105</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>PROCMEAT_0704</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Intake of processed or preserved meat [g/d]</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>ACTIVE_P2</t>
-        </is>
-      </c>
-      <c r="B107">
-        <v>106</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>COFFEE_130301</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Coffee intake [g/d]</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>ACTIVE_P2</t>
-        </is>
-      </c>
-      <c r="B108">
-        <v>107</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>TEA_130302</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Tea intake [g/d]</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>ACTIVE_P2</t>
-        </is>
-      </c>
-      <c r="B109">
-        <v>108</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>DIETARY_ASSESS_INSTR</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Dietary Assessment Instrument</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
         <is>
           <t>0</t>
         </is>
